--- a/uploads/expRegression.xlsx
+++ b/uploads/expRegression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/PrediKit/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{77D33F13-5239-4DB2-A715-3512D09D3325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69A5A5B7-3212-49F1-9EED-424203A26507}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{77D33F13-5239-4DB2-A715-3512D09D3325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA9603FF-0617-4ACD-9EB7-E1A864B7073A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{3FCB8BB5-2836-44B8-913B-2365A2F1C054}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{3FCB8BB5-2836-44B8-913B-2365A2F1C054}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="4" r:id="rId1"/>
@@ -170,10 +170,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -530,7 +526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85344C32-1C07-433A-AC2A-2A3B006482B1}">
-  <dimension ref="A1:O234"/>
+  <dimension ref="A1:O334"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -11529,6 +11525,4706 @@
       </c>
       <c r="O234">
         <v>26.6</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>353</v>
+      </c>
+      <c r="B235">
+        <v>7.2440000000000004E-2</v>
+      </c>
+      <c r="C235">
+        <v>60</v>
+      </c>
+      <c r="D235">
+        <v>1.69</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="G235">
+        <v>5.8840000000000003</v>
+      </c>
+      <c r="H235">
+        <v>18.5</v>
+      </c>
+      <c r="I235">
+        <v>10.7103</v>
+      </c>
+      <c r="J235">
+        <v>4</v>
+      </c>
+      <c r="K235">
+        <v>411</v>
+      </c>
+      <c r="L235">
+        <v>18.3</v>
+      </c>
+      <c r="M235">
+        <v>392.33</v>
+      </c>
+      <c r="N235">
+        <v>7.79</v>
+      </c>
+      <c r="O235">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>357</v>
+      </c>
+      <c r="B236">
+        <v>8.9829600000000003</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+      <c r="F236">
+        <v>0.77</v>
+      </c>
+      <c r="G236">
+        <v>6.2119999999999997</v>
+      </c>
+      <c r="H236">
+        <v>97.4</v>
+      </c>
+      <c r="I236">
+        <v>2.1221999999999999</v>
+      </c>
+      <c r="J236">
+        <v>24</v>
+      </c>
+      <c r="K236">
+        <v>666</v>
+      </c>
+      <c r="L236">
+        <v>20.2</v>
+      </c>
+      <c r="M236">
+        <v>377.73</v>
+      </c>
+      <c r="N236">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="O236">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>358</v>
+      </c>
+      <c r="B237">
+        <v>3.8496999999999999</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E237">
+        <v>1</v>
+      </c>
+      <c r="F237">
+        <v>0.77</v>
+      </c>
+      <c r="G237">
+        <v>6.3949999999999996</v>
+      </c>
+      <c r="H237">
+        <v>91</v>
+      </c>
+      <c r="I237">
+        <v>2.5051999999999999</v>
+      </c>
+      <c r="J237">
+        <v>24</v>
+      </c>
+      <c r="K237">
+        <v>666</v>
+      </c>
+      <c r="L237">
+        <v>20.2</v>
+      </c>
+      <c r="M237">
+        <v>391.34</v>
+      </c>
+      <c r="N237">
+        <v>13.27</v>
+      </c>
+      <c r="O237">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>359</v>
+      </c>
+      <c r="B238">
+        <v>5.2017699999999998</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
+      <c r="F238">
+        <v>0.77</v>
+      </c>
+      <c r="G238">
+        <v>6.1269999999999998</v>
+      </c>
+      <c r="H238">
+        <v>83.4</v>
+      </c>
+      <c r="I238">
+        <v>2.7227000000000001</v>
+      </c>
+      <c r="J238">
+        <v>24</v>
+      </c>
+      <c r="K238">
+        <v>666</v>
+      </c>
+      <c r="L238">
+        <v>20.2</v>
+      </c>
+      <c r="M238">
+        <v>395.43</v>
+      </c>
+      <c r="N238">
+        <v>11.48</v>
+      </c>
+      <c r="O238">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>360</v>
+      </c>
+      <c r="B239">
+        <v>4.2613099999999999</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
+      <c r="F239">
+        <v>0.77</v>
+      </c>
+      <c r="G239">
+        <v>6.1120000000000001</v>
+      </c>
+      <c r="H239">
+        <v>81.3</v>
+      </c>
+      <c r="I239">
+        <v>2.5091000000000001</v>
+      </c>
+      <c r="J239">
+        <v>24</v>
+      </c>
+      <c r="K239">
+        <v>666</v>
+      </c>
+      <c r="L239">
+        <v>20.2</v>
+      </c>
+      <c r="M239">
+        <v>390.74</v>
+      </c>
+      <c r="N239">
+        <v>12.67</v>
+      </c>
+      <c r="O239">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>361</v>
+      </c>
+      <c r="B240">
+        <v>4.5419200000000002</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>0.77</v>
+      </c>
+      <c r="G240">
+        <v>6.3979999999999997</v>
+      </c>
+      <c r="H240">
+        <v>88</v>
+      </c>
+      <c r="I240">
+        <v>2.5182000000000002</v>
+      </c>
+      <c r="J240">
+        <v>24</v>
+      </c>
+      <c r="K240">
+        <v>666</v>
+      </c>
+      <c r="L240">
+        <v>20.2</v>
+      </c>
+      <c r="M240">
+        <v>374.56</v>
+      </c>
+      <c r="N240">
+        <v>7.79</v>
+      </c>
+      <c r="O240">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>363</v>
+      </c>
+      <c r="B241">
+        <v>3.67822</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+      <c r="F241">
+        <v>0.77</v>
+      </c>
+      <c r="G241">
+        <v>5.3620000000000001</v>
+      </c>
+      <c r="H241">
+        <v>96.2</v>
+      </c>
+      <c r="I241">
+        <v>2.1036000000000001</v>
+      </c>
+      <c r="J241">
+        <v>24</v>
+      </c>
+      <c r="K241">
+        <v>666</v>
+      </c>
+      <c r="L241">
+        <v>20.2</v>
+      </c>
+      <c r="M241">
+        <v>380.79</v>
+      </c>
+      <c r="N241">
+        <v>10.19</v>
+      </c>
+      <c r="O241">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>366</v>
+      </c>
+      <c r="B242">
+        <v>4.5558699999999996</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
+      <c r="F242">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="G242">
+        <v>3.5609999999999999</v>
+      </c>
+      <c r="H242">
+        <v>87.9</v>
+      </c>
+      <c r="I242">
+        <v>1.6132</v>
+      </c>
+      <c r="J242">
+        <v>24</v>
+      </c>
+      <c r="K242">
+        <v>666</v>
+      </c>
+      <c r="L242">
+        <v>20.2</v>
+      </c>
+      <c r="M242">
+        <v>354.7</v>
+      </c>
+      <c r="N242">
+        <v>7.12</v>
+      </c>
+      <c r="O242">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>367</v>
+      </c>
+      <c r="B243">
+        <v>3.6969500000000002</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+      <c r="F243">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="G243">
+        <v>4.9630000000000001</v>
+      </c>
+      <c r="H243">
+        <v>91.4</v>
+      </c>
+      <c r="I243">
+        <v>1.7523</v>
+      </c>
+      <c r="J243">
+        <v>24</v>
+      </c>
+      <c r="K243">
+        <v>666</v>
+      </c>
+      <c r="L243">
+        <v>20.2</v>
+      </c>
+      <c r="M243">
+        <v>316.02999999999997</v>
+      </c>
+      <c r="N243">
+        <v>14</v>
+      </c>
+      <c r="O243">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>368</v>
+      </c>
+      <c r="B244">
+        <v>13.5222</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+      <c r="F244">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="G244">
+        <v>3.863</v>
+      </c>
+      <c r="H244">
+        <v>100</v>
+      </c>
+      <c r="I244">
+        <v>1.5105999999999999</v>
+      </c>
+      <c r="J244">
+        <v>24</v>
+      </c>
+      <c r="K244">
+        <v>666</v>
+      </c>
+      <c r="L244">
+        <v>20.2</v>
+      </c>
+      <c r="M244">
+        <v>131.41999999999999</v>
+      </c>
+      <c r="N244">
+        <v>13.33</v>
+      </c>
+      <c r="O244">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>369</v>
+      </c>
+      <c r="B245">
+        <v>4.8982200000000002</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+      <c r="F245">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="G245">
+        <v>4.97</v>
+      </c>
+      <c r="H245">
+        <v>100</v>
+      </c>
+      <c r="I245">
+        <v>1.3325</v>
+      </c>
+      <c r="J245">
+        <v>24</v>
+      </c>
+      <c r="K245">
+        <v>666</v>
+      </c>
+      <c r="L245">
+        <v>20.2</v>
+      </c>
+      <c r="M245">
+        <v>375.52</v>
+      </c>
+      <c r="N245">
+        <v>3.26</v>
+      </c>
+      <c r="O245">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>371</v>
+      </c>
+      <c r="B246">
+        <v>6.5387599999999999</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+      <c r="F246">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="G246">
+        <v>7.016</v>
+      </c>
+      <c r="H246">
+        <v>97.5</v>
+      </c>
+      <c r="I246">
+        <v>1.2023999999999999</v>
+      </c>
+      <c r="J246">
+        <v>24</v>
+      </c>
+      <c r="K246">
+        <v>666</v>
+      </c>
+      <c r="L246">
+        <v>20.2</v>
+      </c>
+      <c r="M246">
+        <v>392.05</v>
+      </c>
+      <c r="N246">
+        <v>2.96</v>
+      </c>
+      <c r="O246">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <v>372</v>
+      </c>
+      <c r="B247">
+        <v>9.2323000000000004</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E247">
+        <v>0</v>
+      </c>
+      <c r="F247">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="G247">
+        <v>6.2160000000000002</v>
+      </c>
+      <c r="H247">
+        <v>100</v>
+      </c>
+      <c r="I247">
+        <v>1.1691</v>
+      </c>
+      <c r="J247">
+        <v>24</v>
+      </c>
+      <c r="K247">
+        <v>666</v>
+      </c>
+      <c r="L247">
+        <v>20.2</v>
+      </c>
+      <c r="M247">
+        <v>366.15</v>
+      </c>
+      <c r="N247">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="O247">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <v>373</v>
+      </c>
+      <c r="B248">
+        <v>8.2672500000000007</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E248">
+        <v>1</v>
+      </c>
+      <c r="F248">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="G248">
+        <v>5.875</v>
+      </c>
+      <c r="H248">
+        <v>89.6</v>
+      </c>
+      <c r="I248">
+        <v>1.1295999999999999</v>
+      </c>
+      <c r="J248">
+        <v>24</v>
+      </c>
+      <c r="K248">
+        <v>666</v>
+      </c>
+      <c r="L248">
+        <v>20.2</v>
+      </c>
+      <c r="M248">
+        <v>347.88</v>
+      </c>
+      <c r="N248">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="O248">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <v>374</v>
+      </c>
+      <c r="B249">
+        <v>11.1081</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
+      <c r="F249">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="G249">
+        <v>4.9059999999999997</v>
+      </c>
+      <c r="H249">
+        <v>100</v>
+      </c>
+      <c r="I249">
+        <v>1.1741999999999999</v>
+      </c>
+      <c r="J249">
+        <v>24</v>
+      </c>
+      <c r="K249">
+        <v>666</v>
+      </c>
+      <c r="L249">
+        <v>20.2</v>
+      </c>
+      <c r="M249">
+        <v>396.9</v>
+      </c>
+      <c r="N249">
+        <v>34.770000000000003</v>
+      </c>
+      <c r="O249">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <v>375</v>
+      </c>
+      <c r="B250">
+        <v>18.498200000000001</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E250">
+        <v>0</v>
+      </c>
+      <c r="F250">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="G250">
+        <v>4.1379999999999999</v>
+      </c>
+      <c r="H250">
+        <v>100</v>
+      </c>
+      <c r="I250">
+        <v>1.137</v>
+      </c>
+      <c r="J250">
+        <v>24</v>
+      </c>
+      <c r="K250">
+        <v>666</v>
+      </c>
+      <c r="L250">
+        <v>20.2</v>
+      </c>
+      <c r="M250">
+        <v>396.9</v>
+      </c>
+      <c r="N250">
+        <v>37.97</v>
+      </c>
+      <c r="O250">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <v>377</v>
+      </c>
+      <c r="B251">
+        <v>15.288</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+      <c r="F251">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="G251">
+        <v>6.649</v>
+      </c>
+      <c r="H251">
+        <v>93.3</v>
+      </c>
+      <c r="I251">
+        <v>1.3449</v>
+      </c>
+      <c r="J251">
+        <v>24</v>
+      </c>
+      <c r="K251">
+        <v>666</v>
+      </c>
+      <c r="L251">
+        <v>20.2</v>
+      </c>
+      <c r="M251">
+        <v>363.02</v>
+      </c>
+      <c r="N251">
+        <v>23.24</v>
+      </c>
+      <c r="O251">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <v>378</v>
+      </c>
+      <c r="B252">
+        <v>9.8234899999999996</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="G252">
+        <v>6.7939999999999996</v>
+      </c>
+      <c r="H252">
+        <v>98.8</v>
+      </c>
+      <c r="I252">
+        <v>1.3580000000000001</v>
+      </c>
+      <c r="J252">
+        <v>24</v>
+      </c>
+      <c r="K252">
+        <v>666</v>
+      </c>
+      <c r="L252">
+        <v>20.2</v>
+      </c>
+      <c r="M252">
+        <v>396.9</v>
+      </c>
+      <c r="N252">
+        <v>21.24</v>
+      </c>
+      <c r="O252">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <v>383</v>
+      </c>
+      <c r="B253">
+        <v>9.1870200000000004</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>0.7</v>
+      </c>
+      <c r="G253">
+        <v>5.5359999999999996</v>
+      </c>
+      <c r="H253">
+        <v>100</v>
+      </c>
+      <c r="I253">
+        <v>1.5804</v>
+      </c>
+      <c r="J253">
+        <v>24</v>
+      </c>
+      <c r="K253">
+        <v>666</v>
+      </c>
+      <c r="L253">
+        <v>20.2</v>
+      </c>
+      <c r="M253">
+        <v>396.9</v>
+      </c>
+      <c r="N253">
+        <v>23.6</v>
+      </c>
+      <c r="O253">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>384</v>
+      </c>
+      <c r="B254">
+        <v>7.9924799999999996</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+      <c r="F254">
+        <v>0.7</v>
+      </c>
+      <c r="G254">
+        <v>5.52</v>
+      </c>
+      <c r="H254">
+        <v>100</v>
+      </c>
+      <c r="I254">
+        <v>1.5330999999999999</v>
+      </c>
+      <c r="J254">
+        <v>24</v>
+      </c>
+      <c r="K254">
+        <v>666</v>
+      </c>
+      <c r="L254">
+        <v>20.2</v>
+      </c>
+      <c r="M254">
+        <v>396.9</v>
+      </c>
+      <c r="N254">
+        <v>24.56</v>
+      </c>
+      <c r="O254">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>385</v>
+      </c>
+      <c r="B255">
+        <v>20.084900000000001</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>0.7</v>
+      </c>
+      <c r="G255">
+        <v>4.3680000000000003</v>
+      </c>
+      <c r="H255">
+        <v>91.2</v>
+      </c>
+      <c r="I255">
+        <v>1.4395</v>
+      </c>
+      <c r="J255">
+        <v>24</v>
+      </c>
+      <c r="K255">
+        <v>666</v>
+      </c>
+      <c r="L255">
+        <v>20.2</v>
+      </c>
+      <c r="M255">
+        <v>285.83</v>
+      </c>
+      <c r="N255">
+        <v>30.63</v>
+      </c>
+      <c r="O255">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>387</v>
+      </c>
+      <c r="B256">
+        <v>24.393799999999999</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>0.7</v>
+      </c>
+      <c r="G256">
+        <v>4.6520000000000001</v>
+      </c>
+      <c r="H256">
+        <v>100</v>
+      </c>
+      <c r="I256">
+        <v>1.4672000000000001</v>
+      </c>
+      <c r="J256">
+        <v>24</v>
+      </c>
+      <c r="K256">
+        <v>666</v>
+      </c>
+      <c r="L256">
+        <v>20.2</v>
+      </c>
+      <c r="M256">
+        <v>396.9</v>
+      </c>
+      <c r="N256">
+        <v>28.28</v>
+      </c>
+      <c r="O256">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <v>388</v>
+      </c>
+      <c r="B257">
+        <v>22.597100000000001</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>0.7</v>
+      </c>
+      <c r="G257">
+        <v>5</v>
+      </c>
+      <c r="H257">
+        <v>89.5</v>
+      </c>
+      <c r="I257">
+        <v>1.5184</v>
+      </c>
+      <c r="J257">
+        <v>24</v>
+      </c>
+      <c r="K257">
+        <v>666</v>
+      </c>
+      <c r="L257">
+        <v>20.2</v>
+      </c>
+      <c r="M257">
+        <v>396.9</v>
+      </c>
+      <c r="N257">
+        <v>31.99</v>
+      </c>
+      <c r="O257">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <v>390</v>
+      </c>
+      <c r="B258">
+        <v>8.1517400000000002</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>0.7</v>
+      </c>
+      <c r="G258">
+        <v>5.39</v>
+      </c>
+      <c r="H258">
+        <v>98.9</v>
+      </c>
+      <c r="I258">
+        <v>1.7281</v>
+      </c>
+      <c r="J258">
+        <v>24</v>
+      </c>
+      <c r="K258">
+        <v>666</v>
+      </c>
+      <c r="L258">
+        <v>20.2</v>
+      </c>
+      <c r="M258">
+        <v>396.9</v>
+      </c>
+      <c r="N258">
+        <v>20.85</v>
+      </c>
+      <c r="O258">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <v>392</v>
+      </c>
+      <c r="B259">
+        <v>5.29305</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>0.7</v>
+      </c>
+      <c r="G259">
+        <v>6.0510000000000002</v>
+      </c>
+      <c r="H259">
+        <v>82.5</v>
+      </c>
+      <c r="I259">
+        <v>2.1678000000000002</v>
+      </c>
+      <c r="J259">
+        <v>24</v>
+      </c>
+      <c r="K259">
+        <v>666</v>
+      </c>
+      <c r="L259">
+        <v>20.2</v>
+      </c>
+      <c r="M259">
+        <v>378.38</v>
+      </c>
+      <c r="N259">
+        <v>18.760000000000002</v>
+      </c>
+      <c r="O259">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <v>393</v>
+      </c>
+      <c r="B260">
+        <v>11.5779</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>0.7</v>
+      </c>
+      <c r="G260">
+        <v>5.0359999999999996</v>
+      </c>
+      <c r="H260">
+        <v>97</v>
+      </c>
+      <c r="I260">
+        <v>1.77</v>
+      </c>
+      <c r="J260">
+        <v>24</v>
+      </c>
+      <c r="K260">
+        <v>666</v>
+      </c>
+      <c r="L260">
+        <v>20.2</v>
+      </c>
+      <c r="M260">
+        <v>396.9</v>
+      </c>
+      <c r="N260">
+        <v>25.68</v>
+      </c>
+      <c r="O260">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <v>395</v>
+      </c>
+      <c r="B261">
+        <v>13.3598</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="G261">
+        <v>5.8869999999999996</v>
+      </c>
+      <c r="H261">
+        <v>94.7</v>
+      </c>
+      <c r="I261">
+        <v>1.7821</v>
+      </c>
+      <c r="J261">
+        <v>24</v>
+      </c>
+      <c r="K261">
+        <v>666</v>
+      </c>
+      <c r="L261">
+        <v>20.2</v>
+      </c>
+      <c r="M261">
+        <v>396.9</v>
+      </c>
+      <c r="N261">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="O261">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <v>397</v>
+      </c>
+      <c r="B262">
+        <v>5.8720499999999998</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="G262">
+        <v>6.4050000000000002</v>
+      </c>
+      <c r="H262">
+        <v>96</v>
+      </c>
+      <c r="I262">
+        <v>1.6768000000000001</v>
+      </c>
+      <c r="J262">
+        <v>24</v>
+      </c>
+      <c r="K262">
+        <v>666</v>
+      </c>
+      <c r="L262">
+        <v>20.2</v>
+      </c>
+      <c r="M262">
+        <v>396.9</v>
+      </c>
+      <c r="N262">
+        <v>19.37</v>
+      </c>
+      <c r="O262">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A263">
+        <v>399</v>
+      </c>
+      <c r="B263">
+        <v>38.351799999999997</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="G263">
+        <v>5.4530000000000003</v>
+      </c>
+      <c r="H263">
+        <v>100</v>
+      </c>
+      <c r="I263">
+        <v>1.4896</v>
+      </c>
+      <c r="J263">
+        <v>24</v>
+      </c>
+      <c r="K263">
+        <v>666</v>
+      </c>
+      <c r="L263">
+        <v>20.2</v>
+      </c>
+      <c r="M263">
+        <v>396.9</v>
+      </c>
+      <c r="N263">
+        <v>30.59</v>
+      </c>
+      <c r="O263">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <v>401</v>
+      </c>
+      <c r="B264">
+        <v>25.046099999999999</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="G264">
+        <v>5.9870000000000001</v>
+      </c>
+      <c r="H264">
+        <v>100</v>
+      </c>
+      <c r="I264">
+        <v>1.5888</v>
+      </c>
+      <c r="J264">
+        <v>24</v>
+      </c>
+      <c r="K264">
+        <v>666</v>
+      </c>
+      <c r="L264">
+        <v>20.2</v>
+      </c>
+      <c r="M264">
+        <v>396.9</v>
+      </c>
+      <c r="N264">
+        <v>26.77</v>
+      </c>
+      <c r="O264">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <v>402</v>
+      </c>
+      <c r="B265">
+        <v>14.2362</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="G265">
+        <v>6.343</v>
+      </c>
+      <c r="H265">
+        <v>100</v>
+      </c>
+      <c r="I265">
+        <v>1.5741000000000001</v>
+      </c>
+      <c r="J265">
+        <v>24</v>
+      </c>
+      <c r="K265">
+        <v>666</v>
+      </c>
+      <c r="L265">
+        <v>20.2</v>
+      </c>
+      <c r="M265">
+        <v>396.9</v>
+      </c>
+      <c r="N265">
+        <v>20.32</v>
+      </c>
+      <c r="O265">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <v>404</v>
+      </c>
+      <c r="B266">
+        <v>24.8017</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="G266">
+        <v>5.3490000000000002</v>
+      </c>
+      <c r="H266">
+        <v>96</v>
+      </c>
+      <c r="I266">
+        <v>1.7028000000000001</v>
+      </c>
+      <c r="J266">
+        <v>24</v>
+      </c>
+      <c r="K266">
+        <v>666</v>
+      </c>
+      <c r="L266">
+        <v>20.2</v>
+      </c>
+      <c r="M266">
+        <v>396.9</v>
+      </c>
+      <c r="N266">
+        <v>19.77</v>
+      </c>
+      <c r="O266">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>408</v>
+      </c>
+      <c r="B267">
+        <v>11.9511</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="G267">
+        <v>5.6079999999999997</v>
+      </c>
+      <c r="H267">
+        <v>100</v>
+      </c>
+      <c r="I267">
+        <v>1.2851999999999999</v>
+      </c>
+      <c r="J267">
+        <v>24</v>
+      </c>
+      <c r="K267">
+        <v>666</v>
+      </c>
+      <c r="L267">
+        <v>20.2</v>
+      </c>
+      <c r="M267">
+        <v>332.09</v>
+      </c>
+      <c r="N267">
+        <v>12.13</v>
+      </c>
+      <c r="O267">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>409</v>
+      </c>
+      <c r="B268">
+        <v>7.4038899999999996</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="G268">
+        <v>5.617</v>
+      </c>
+      <c r="H268">
+        <v>97.9</v>
+      </c>
+      <c r="I268">
+        <v>1.4547000000000001</v>
+      </c>
+      <c r="J268">
+        <v>24</v>
+      </c>
+      <c r="K268">
+        <v>666</v>
+      </c>
+      <c r="L268">
+        <v>20.2</v>
+      </c>
+      <c r="M268">
+        <v>314.64</v>
+      </c>
+      <c r="N268">
+        <v>26.4</v>
+      </c>
+      <c r="O268">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>414</v>
+      </c>
+      <c r="B269">
+        <v>28.655799999999999</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="G269">
+        <v>5.1550000000000002</v>
+      </c>
+      <c r="H269">
+        <v>100</v>
+      </c>
+      <c r="I269">
+        <v>1.5893999999999999</v>
+      </c>
+      <c r="J269">
+        <v>24</v>
+      </c>
+      <c r="K269">
+        <v>666</v>
+      </c>
+      <c r="L269">
+        <v>20.2</v>
+      </c>
+      <c r="M269">
+        <v>210.97</v>
+      </c>
+      <c r="N269">
+        <v>20.079999999999998</v>
+      </c>
+      <c r="O269">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <v>415</v>
+      </c>
+      <c r="B270">
+        <v>45.746099999999998</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="G270">
+        <v>4.5190000000000001</v>
+      </c>
+      <c r="H270">
+        <v>100</v>
+      </c>
+      <c r="I270">
+        <v>1.6581999999999999</v>
+      </c>
+      <c r="J270">
+        <v>24</v>
+      </c>
+      <c r="K270">
+        <v>666</v>
+      </c>
+      <c r="L270">
+        <v>20.2</v>
+      </c>
+      <c r="M270">
+        <v>88.27</v>
+      </c>
+      <c r="N270">
+        <v>36.979999999999997</v>
+      </c>
+      <c r="O270">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <v>416</v>
+      </c>
+      <c r="B271">
+        <v>18.084599999999998</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="G271">
+        <v>6.4340000000000002</v>
+      </c>
+      <c r="H271">
+        <v>100</v>
+      </c>
+      <c r="I271">
+        <v>1.8347</v>
+      </c>
+      <c r="J271">
+        <v>24</v>
+      </c>
+      <c r="K271">
+        <v>666</v>
+      </c>
+      <c r="L271">
+        <v>20.2</v>
+      </c>
+      <c r="M271">
+        <v>27.25</v>
+      </c>
+      <c r="N271">
+        <v>29.05</v>
+      </c>
+      <c r="O271">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <v>418</v>
+      </c>
+      <c r="B272">
+        <v>25.9406</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="G272">
+        <v>5.3040000000000003</v>
+      </c>
+      <c r="H272">
+        <v>89.1</v>
+      </c>
+      <c r="I272">
+        <v>1.6475</v>
+      </c>
+      <c r="J272">
+        <v>24</v>
+      </c>
+      <c r="K272">
+        <v>666</v>
+      </c>
+      <c r="L272">
+        <v>20.2</v>
+      </c>
+      <c r="M272">
+        <v>127.36</v>
+      </c>
+      <c r="N272">
+        <v>26.64</v>
+      </c>
+      <c r="O272">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <v>419</v>
+      </c>
+      <c r="B273">
+        <v>73.534099999999995</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="G273">
+        <v>5.9569999999999999</v>
+      </c>
+      <c r="H273">
+        <v>100</v>
+      </c>
+      <c r="I273">
+        <v>1.8026</v>
+      </c>
+      <c r="J273">
+        <v>24</v>
+      </c>
+      <c r="K273">
+        <v>666</v>
+      </c>
+      <c r="L273">
+        <v>20.2</v>
+      </c>
+      <c r="M273">
+        <v>16.45</v>
+      </c>
+      <c r="N273">
+        <v>20.62</v>
+      </c>
+      <c r="O273">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <v>420</v>
+      </c>
+      <c r="B274">
+        <v>11.8123</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="G274">
+        <v>6.8239999999999998</v>
+      </c>
+      <c r="H274">
+        <v>76.5</v>
+      </c>
+      <c r="I274">
+        <v>1.794</v>
+      </c>
+      <c r="J274">
+        <v>24</v>
+      </c>
+      <c r="K274">
+        <v>666</v>
+      </c>
+      <c r="L274">
+        <v>20.2</v>
+      </c>
+      <c r="M274">
+        <v>48.45</v>
+      </c>
+      <c r="N274">
+        <v>22.74</v>
+      </c>
+      <c r="O274">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <v>425</v>
+      </c>
+      <c r="B275">
+        <v>8.7921200000000006</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="G275">
+        <v>5.5650000000000004</v>
+      </c>
+      <c r="H275">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="I275">
+        <v>2.0634999999999999</v>
+      </c>
+      <c r="J275">
+        <v>24</v>
+      </c>
+      <c r="K275">
+        <v>666</v>
+      </c>
+      <c r="L275">
+        <v>20.2</v>
+      </c>
+      <c r="M275">
+        <v>3.65</v>
+      </c>
+      <c r="N275">
+        <v>17.16</v>
+      </c>
+      <c r="O275">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <v>426</v>
+      </c>
+      <c r="B276">
+        <v>15.860300000000001</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="G276">
+        <v>5.8959999999999999</v>
+      </c>
+      <c r="H276">
+        <v>95.4</v>
+      </c>
+      <c r="I276">
+        <v>1.9096</v>
+      </c>
+      <c r="J276">
+        <v>24</v>
+      </c>
+      <c r="K276">
+        <v>666</v>
+      </c>
+      <c r="L276">
+        <v>20.2</v>
+      </c>
+      <c r="M276">
+        <v>7.68</v>
+      </c>
+      <c r="N276">
+        <v>24.39</v>
+      </c>
+      <c r="O276">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <v>428</v>
+      </c>
+      <c r="B277">
+        <v>37.661900000000003</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="G277">
+        <v>6.202</v>
+      </c>
+      <c r="H277">
+        <v>78.7</v>
+      </c>
+      <c r="I277">
+        <v>1.8629</v>
+      </c>
+      <c r="J277">
+        <v>24</v>
+      </c>
+      <c r="K277">
+        <v>666</v>
+      </c>
+      <c r="L277">
+        <v>20.2</v>
+      </c>
+      <c r="M277">
+        <v>18.82</v>
+      </c>
+      <c r="N277">
+        <v>14.52</v>
+      </c>
+      <c r="O277">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <v>429</v>
+      </c>
+      <c r="B278">
+        <v>7.3671100000000003</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="G278">
+        <v>6.1929999999999996</v>
+      </c>
+      <c r="H278">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="I278">
+        <v>1.9356</v>
+      </c>
+      <c r="J278">
+        <v>24</v>
+      </c>
+      <c r="K278">
+        <v>666</v>
+      </c>
+      <c r="L278">
+        <v>20.2</v>
+      </c>
+      <c r="M278">
+        <v>96.73</v>
+      </c>
+      <c r="N278">
+        <v>21.52</v>
+      </c>
+      <c r="O278">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>430</v>
+      </c>
+      <c r="B279">
+        <v>9.3388899999999992</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="G279">
+        <v>6.38</v>
+      </c>
+      <c r="H279">
+        <v>95.6</v>
+      </c>
+      <c r="I279">
+        <v>1.9681999999999999</v>
+      </c>
+      <c r="J279">
+        <v>24</v>
+      </c>
+      <c r="K279">
+        <v>666</v>
+      </c>
+      <c r="L279">
+        <v>20.2</v>
+      </c>
+      <c r="M279">
+        <v>60.72</v>
+      </c>
+      <c r="N279">
+        <v>24.08</v>
+      </c>
+      <c r="O279">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>432</v>
+      </c>
+      <c r="B280">
+        <v>10.0623</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="G280">
+        <v>6.8330000000000002</v>
+      </c>
+      <c r="H280">
+        <v>94.3</v>
+      </c>
+      <c r="I280">
+        <v>2.0882000000000001</v>
+      </c>
+      <c r="J280">
+        <v>24</v>
+      </c>
+      <c r="K280">
+        <v>666</v>
+      </c>
+      <c r="L280">
+        <v>20.2</v>
+      </c>
+      <c r="M280">
+        <v>81.33</v>
+      </c>
+      <c r="N280">
+        <v>19.690000000000001</v>
+      </c>
+      <c r="O280">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>433</v>
+      </c>
+      <c r="B281">
+        <v>6.4440499999999998</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="G281">
+        <v>6.4249999999999998</v>
+      </c>
+      <c r="H281">
+        <v>74.8</v>
+      </c>
+      <c r="I281">
+        <v>2.2004000000000001</v>
+      </c>
+      <c r="J281">
+        <v>24</v>
+      </c>
+      <c r="K281">
+        <v>666</v>
+      </c>
+      <c r="L281">
+        <v>20.2</v>
+      </c>
+      <c r="M281">
+        <v>97.95</v>
+      </c>
+      <c r="N281">
+        <v>12.03</v>
+      </c>
+      <c r="O281">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>434</v>
+      </c>
+      <c r="B282">
+        <v>5.5810700000000004</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G282">
+        <v>6.4359999999999999</v>
+      </c>
+      <c r="H282">
+        <v>87.9</v>
+      </c>
+      <c r="I282">
+        <v>2.3157999999999999</v>
+      </c>
+      <c r="J282">
+        <v>24</v>
+      </c>
+      <c r="K282">
+        <v>666</v>
+      </c>
+      <c r="L282">
+        <v>20.2</v>
+      </c>
+      <c r="M282">
+        <v>100.19</v>
+      </c>
+      <c r="N282">
+        <v>16.22</v>
+      </c>
+      <c r="O282">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>435</v>
+      </c>
+      <c r="B283">
+        <v>13.913399999999999</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G283">
+        <v>6.2080000000000002</v>
+      </c>
+      <c r="H283">
+        <v>95</v>
+      </c>
+      <c r="I283">
+        <v>2.2222</v>
+      </c>
+      <c r="J283">
+        <v>24</v>
+      </c>
+      <c r="K283">
+        <v>666</v>
+      </c>
+      <c r="L283">
+        <v>20.2</v>
+      </c>
+      <c r="M283">
+        <v>100.63</v>
+      </c>
+      <c r="N283">
+        <v>15.17</v>
+      </c>
+      <c r="O283">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>438</v>
+      </c>
+      <c r="B284">
+        <v>15.177199999999999</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>0.74</v>
+      </c>
+      <c r="G284">
+        <v>6.1520000000000001</v>
+      </c>
+      <c r="H284">
+        <v>100</v>
+      </c>
+      <c r="I284">
+        <v>1.9141999999999999</v>
+      </c>
+      <c r="J284">
+        <v>24</v>
+      </c>
+      <c r="K284">
+        <v>666</v>
+      </c>
+      <c r="L284">
+        <v>20.2</v>
+      </c>
+      <c r="M284">
+        <v>9.32</v>
+      </c>
+      <c r="N284">
+        <v>26.45</v>
+      </c>
+      <c r="O284">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>440</v>
+      </c>
+      <c r="B285">
+        <v>9.3906299999999998</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>0.74</v>
+      </c>
+      <c r="G285">
+        <v>5.6269999999999998</v>
+      </c>
+      <c r="H285">
+        <v>93.9</v>
+      </c>
+      <c r="I285">
+        <v>1.8171999999999999</v>
+      </c>
+      <c r="J285">
+        <v>24</v>
+      </c>
+      <c r="K285">
+        <v>666</v>
+      </c>
+      <c r="L285">
+        <v>20.2</v>
+      </c>
+      <c r="M285">
+        <v>396.9</v>
+      </c>
+      <c r="N285">
+        <v>22.88</v>
+      </c>
+      <c r="O285">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>441</v>
+      </c>
+      <c r="B286">
+        <v>22.051100000000002</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>0.74</v>
+      </c>
+      <c r="G286">
+        <v>5.8179999999999996</v>
+      </c>
+      <c r="H286">
+        <v>92.4</v>
+      </c>
+      <c r="I286">
+        <v>1.8662000000000001</v>
+      </c>
+      <c r="J286">
+        <v>24</v>
+      </c>
+      <c r="K286">
+        <v>666</v>
+      </c>
+      <c r="L286">
+        <v>20.2</v>
+      </c>
+      <c r="M286">
+        <v>391.45</v>
+      </c>
+      <c r="N286">
+        <v>22.11</v>
+      </c>
+      <c r="O286">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <v>442</v>
+      </c>
+      <c r="B287">
+        <v>9.7241800000000005</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>0.74</v>
+      </c>
+      <c r="G287">
+        <v>6.4059999999999997</v>
+      </c>
+      <c r="H287">
+        <v>97.2</v>
+      </c>
+      <c r="I287">
+        <v>2.0651000000000002</v>
+      </c>
+      <c r="J287">
+        <v>24</v>
+      </c>
+      <c r="K287">
+        <v>666</v>
+      </c>
+      <c r="L287">
+        <v>20.2</v>
+      </c>
+      <c r="M287">
+        <v>385.96</v>
+      </c>
+      <c r="N287">
+        <v>19.52</v>
+      </c>
+      <c r="O287">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <v>443</v>
+      </c>
+      <c r="B288">
+        <v>5.6663699999999997</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>0.74</v>
+      </c>
+      <c r="G288">
+        <v>6.2190000000000003</v>
+      </c>
+      <c r="H288">
+        <v>100</v>
+      </c>
+      <c r="I288">
+        <v>2.0047999999999999</v>
+      </c>
+      <c r="J288">
+        <v>24</v>
+      </c>
+      <c r="K288">
+        <v>666</v>
+      </c>
+      <c r="L288">
+        <v>20.2</v>
+      </c>
+      <c r="M288">
+        <v>395.69</v>
+      </c>
+      <c r="N288">
+        <v>16.59</v>
+      </c>
+      <c r="O288">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <v>444</v>
+      </c>
+      <c r="B289">
+        <v>9.9665400000000002</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>0.74</v>
+      </c>
+      <c r="G289">
+        <v>6.4850000000000003</v>
+      </c>
+      <c r="H289">
+        <v>100</v>
+      </c>
+      <c r="I289">
+        <v>1.9783999999999999</v>
+      </c>
+      <c r="J289">
+        <v>24</v>
+      </c>
+      <c r="K289">
+        <v>666</v>
+      </c>
+      <c r="L289">
+        <v>20.2</v>
+      </c>
+      <c r="M289">
+        <v>386.73</v>
+      </c>
+      <c r="N289">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="O289">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <v>445</v>
+      </c>
+      <c r="B290">
+        <v>12.802300000000001</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E290">
+        <v>0</v>
+      </c>
+      <c r="F290">
+        <v>0.74</v>
+      </c>
+      <c r="G290">
+        <v>5.8540000000000001</v>
+      </c>
+      <c r="H290">
+        <v>96.6</v>
+      </c>
+      <c r="I290">
+        <v>1.8956</v>
+      </c>
+      <c r="J290">
+        <v>24</v>
+      </c>
+      <c r="K290">
+        <v>666</v>
+      </c>
+      <c r="L290">
+        <v>20.2</v>
+      </c>
+      <c r="M290">
+        <v>240.52</v>
+      </c>
+      <c r="N290">
+        <v>23.79</v>
+      </c>
+      <c r="O290">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <v>446</v>
+      </c>
+      <c r="B291">
+        <v>10.671799999999999</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="F291">
+        <v>0.74</v>
+      </c>
+      <c r="G291">
+        <v>6.4589999999999996</v>
+      </c>
+      <c r="H291">
+        <v>94.8</v>
+      </c>
+      <c r="I291">
+        <v>1.9879</v>
+      </c>
+      <c r="J291">
+        <v>24</v>
+      </c>
+      <c r="K291">
+        <v>666</v>
+      </c>
+      <c r="L291">
+        <v>20.2</v>
+      </c>
+      <c r="M291">
+        <v>43.06</v>
+      </c>
+      <c r="N291">
+        <v>23.98</v>
+      </c>
+      <c r="O291">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>448</v>
+      </c>
+      <c r="B292">
+        <v>9.9248499999999993</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
+      <c r="F292">
+        <v>0.74</v>
+      </c>
+      <c r="G292">
+        <v>6.2510000000000003</v>
+      </c>
+      <c r="H292">
+        <v>96.6</v>
+      </c>
+      <c r="I292">
+        <v>2.198</v>
+      </c>
+      <c r="J292">
+        <v>24</v>
+      </c>
+      <c r="K292">
+        <v>666</v>
+      </c>
+      <c r="L292">
+        <v>20.2</v>
+      </c>
+      <c r="M292">
+        <v>388.52</v>
+      </c>
+      <c r="N292">
+        <v>16.440000000000001</v>
+      </c>
+      <c r="O292">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>449</v>
+      </c>
+      <c r="B293">
+        <v>9.3290900000000008</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G293">
+        <v>6.1849999999999996</v>
+      </c>
+      <c r="H293">
+        <v>98.7</v>
+      </c>
+      <c r="I293">
+        <v>2.2616000000000001</v>
+      </c>
+      <c r="J293">
+        <v>24</v>
+      </c>
+      <c r="K293">
+        <v>666</v>
+      </c>
+      <c r="L293">
+        <v>20.2</v>
+      </c>
+      <c r="M293">
+        <v>396.9</v>
+      </c>
+      <c r="N293">
+        <v>18.13</v>
+      </c>
+      <c r="O293">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>452</v>
+      </c>
+      <c r="B294">
+        <v>5.4411399999999999</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G294">
+        <v>6.6550000000000002</v>
+      </c>
+      <c r="H294">
+        <v>98.2</v>
+      </c>
+      <c r="I294">
+        <v>2.3552</v>
+      </c>
+      <c r="J294">
+        <v>24</v>
+      </c>
+      <c r="K294">
+        <v>666</v>
+      </c>
+      <c r="L294">
+        <v>20.2</v>
+      </c>
+      <c r="M294">
+        <v>355.29</v>
+      </c>
+      <c r="N294">
+        <v>17.73</v>
+      </c>
+      <c r="O294">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <v>453</v>
+      </c>
+      <c r="B295">
+        <v>5.0901699999999996</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G295">
+        <v>6.2969999999999997</v>
+      </c>
+      <c r="H295">
+        <v>91.8</v>
+      </c>
+      <c r="I295">
+        <v>2.3681999999999999</v>
+      </c>
+      <c r="J295">
+        <v>24</v>
+      </c>
+      <c r="K295">
+        <v>666</v>
+      </c>
+      <c r="L295">
+        <v>20.2</v>
+      </c>
+      <c r="M295">
+        <v>385.09</v>
+      </c>
+      <c r="N295">
+        <v>17.27</v>
+      </c>
+      <c r="O295">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <v>454</v>
+      </c>
+      <c r="B296">
+        <v>8.2480899999999995</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G296">
+        <v>7.3929999999999998</v>
+      </c>
+      <c r="H296">
+        <v>99.3</v>
+      </c>
+      <c r="I296">
+        <v>2.4527000000000001</v>
+      </c>
+      <c r="J296">
+        <v>24</v>
+      </c>
+      <c r="K296">
+        <v>666</v>
+      </c>
+      <c r="L296">
+        <v>20.2</v>
+      </c>
+      <c r="M296">
+        <v>375.87</v>
+      </c>
+      <c r="N296">
+        <v>16.739999999999998</v>
+      </c>
+      <c r="O296">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <v>456</v>
+      </c>
+      <c r="B297">
+        <v>4.75237</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+      <c r="F297">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G297">
+        <v>6.5250000000000004</v>
+      </c>
+      <c r="H297">
+        <v>86.5</v>
+      </c>
+      <c r="I297">
+        <v>2.4358</v>
+      </c>
+      <c r="J297">
+        <v>24</v>
+      </c>
+      <c r="K297">
+        <v>666</v>
+      </c>
+      <c r="L297">
+        <v>20.2</v>
+      </c>
+      <c r="M297">
+        <v>50.92</v>
+      </c>
+      <c r="N297">
+        <v>18.13</v>
+      </c>
+      <c r="O297">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <v>458</v>
+      </c>
+      <c r="B298">
+        <v>8.2005800000000004</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G298">
+        <v>5.9359999999999999</v>
+      </c>
+      <c r="H298">
+        <v>80.3</v>
+      </c>
+      <c r="I298">
+        <v>2.7791999999999999</v>
+      </c>
+      <c r="J298">
+        <v>24</v>
+      </c>
+      <c r="K298">
+        <v>666</v>
+      </c>
+      <c r="L298">
+        <v>20.2</v>
+      </c>
+      <c r="M298">
+        <v>3.5</v>
+      </c>
+      <c r="N298">
+        <v>16.940000000000001</v>
+      </c>
+      <c r="O298">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <v>459</v>
+      </c>
+      <c r="B299">
+        <v>7.75223</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G299">
+        <v>6.3010000000000002</v>
+      </c>
+      <c r="H299">
+        <v>83.7</v>
+      </c>
+      <c r="I299">
+        <v>2.7831000000000001</v>
+      </c>
+      <c r="J299">
+        <v>24</v>
+      </c>
+      <c r="K299">
+        <v>666</v>
+      </c>
+      <c r="L299">
+        <v>20.2</v>
+      </c>
+      <c r="M299">
+        <v>272.20999999999998</v>
+      </c>
+      <c r="N299">
+        <v>16.23</v>
+      </c>
+      <c r="O299">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <v>460</v>
+      </c>
+      <c r="B300">
+        <v>6.8011699999999999</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
+      <c r="F300">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G300">
+        <v>6.0810000000000004</v>
+      </c>
+      <c r="H300">
+        <v>84.4</v>
+      </c>
+      <c r="I300">
+        <v>2.7174999999999998</v>
+      </c>
+      <c r="J300">
+        <v>24</v>
+      </c>
+      <c r="K300">
+        <v>666</v>
+      </c>
+      <c r="L300">
+        <v>20.2</v>
+      </c>
+      <c r="M300">
+        <v>396.9</v>
+      </c>
+      <c r="N300">
+        <v>14.7</v>
+      </c>
+      <c r="O300">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <v>461</v>
+      </c>
+      <c r="B301">
+        <v>4.8121299999999998</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
+      <c r="F301">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G301">
+        <v>6.7009999999999996</v>
+      </c>
+      <c r="H301">
+        <v>90</v>
+      </c>
+      <c r="I301">
+        <v>2.5975000000000001</v>
+      </c>
+      <c r="J301">
+        <v>24</v>
+      </c>
+      <c r="K301">
+        <v>666</v>
+      </c>
+      <c r="L301">
+        <v>20.2</v>
+      </c>
+      <c r="M301">
+        <v>255.23</v>
+      </c>
+      <c r="N301">
+        <v>16.420000000000002</v>
+      </c>
+      <c r="O301">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A302">
+        <v>462</v>
+      </c>
+      <c r="B302">
+        <v>3.6931099999999999</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G302">
+        <v>6.3760000000000003</v>
+      </c>
+      <c r="H302">
+        <v>88.4</v>
+      </c>
+      <c r="I302">
+        <v>2.5670999999999999</v>
+      </c>
+      <c r="J302">
+        <v>24</v>
+      </c>
+      <c r="K302">
+        <v>666</v>
+      </c>
+      <c r="L302">
+        <v>20.2</v>
+      </c>
+      <c r="M302">
+        <v>391.43</v>
+      </c>
+      <c r="N302">
+        <v>14.65</v>
+      </c>
+      <c r="O302">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <v>463</v>
+      </c>
+      <c r="B303">
+        <v>6.6549199999999997</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G303">
+        <v>6.3170000000000002</v>
+      </c>
+      <c r="H303">
+        <v>83</v>
+      </c>
+      <c r="I303">
+        <v>2.7343999999999999</v>
+      </c>
+      <c r="J303">
+        <v>24</v>
+      </c>
+      <c r="K303">
+        <v>666</v>
+      </c>
+      <c r="L303">
+        <v>20.2</v>
+      </c>
+      <c r="M303">
+        <v>396.9</v>
+      </c>
+      <c r="N303">
+        <v>13.99</v>
+      </c>
+      <c r="O303">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <v>464</v>
+      </c>
+      <c r="B304">
+        <v>5.8211500000000003</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
+      <c r="F304">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="G304">
+        <v>6.5129999999999999</v>
+      </c>
+      <c r="H304">
+        <v>89.9</v>
+      </c>
+      <c r="I304">
+        <v>2.8016000000000001</v>
+      </c>
+      <c r="J304">
+        <v>24</v>
+      </c>
+      <c r="K304">
+        <v>666</v>
+      </c>
+      <c r="L304">
+        <v>20.2</v>
+      </c>
+      <c r="M304">
+        <v>393.82</v>
+      </c>
+      <c r="N304">
+        <v>10.29</v>
+      </c>
+      <c r="O304">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <v>465</v>
+      </c>
+      <c r="B305">
+        <v>7.8393199999999998</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E305">
+        <v>0</v>
+      </c>
+      <c r="F305">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="G305">
+        <v>6.2089999999999996</v>
+      </c>
+      <c r="H305">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="I305">
+        <v>2.9634</v>
+      </c>
+      <c r="J305">
+        <v>24</v>
+      </c>
+      <c r="K305">
+        <v>666</v>
+      </c>
+      <c r="L305">
+        <v>20.2</v>
+      </c>
+      <c r="M305">
+        <v>396.9</v>
+      </c>
+      <c r="N305">
+        <v>13.22</v>
+      </c>
+      <c r="O305">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <v>466</v>
+      </c>
+      <c r="B306">
+        <v>3.1636000000000002</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E306">
+        <v>0</v>
+      </c>
+      <c r="F306">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="G306">
+        <v>5.7590000000000003</v>
+      </c>
+      <c r="H306">
+        <v>48.2</v>
+      </c>
+      <c r="I306">
+        <v>3.0665</v>
+      </c>
+      <c r="J306">
+        <v>24</v>
+      </c>
+      <c r="K306">
+        <v>666</v>
+      </c>
+      <c r="L306">
+        <v>20.2</v>
+      </c>
+      <c r="M306">
+        <v>334.4</v>
+      </c>
+      <c r="N306">
+        <v>14.13</v>
+      </c>
+      <c r="O306">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A307">
+        <v>467</v>
+      </c>
+      <c r="B307">
+        <v>3.7749799999999998</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
+      <c r="F307">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="G307">
+        <v>5.952</v>
+      </c>
+      <c r="H307">
+        <v>84.7</v>
+      </c>
+      <c r="I307">
+        <v>2.8715000000000002</v>
+      </c>
+      <c r="J307">
+        <v>24</v>
+      </c>
+      <c r="K307">
+        <v>666</v>
+      </c>
+      <c r="L307">
+        <v>20.2</v>
+      </c>
+      <c r="M307">
+        <v>22.01</v>
+      </c>
+      <c r="N307">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="O307">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A308">
+        <v>468</v>
+      </c>
+      <c r="B308">
+        <v>4.4222799999999998</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E308">
+        <v>0</v>
+      </c>
+      <c r="F308">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="G308">
+        <v>6.0030000000000001</v>
+      </c>
+      <c r="H308">
+        <v>94.5</v>
+      </c>
+      <c r="I308">
+        <v>2.5402999999999998</v>
+      </c>
+      <c r="J308">
+        <v>24</v>
+      </c>
+      <c r="K308">
+        <v>666</v>
+      </c>
+      <c r="L308">
+        <v>20.2</v>
+      </c>
+      <c r="M308">
+        <v>331.29</v>
+      </c>
+      <c r="N308">
+        <v>21.32</v>
+      </c>
+      <c r="O308">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A309">
+        <v>469</v>
+      </c>
+      <c r="B309">
+        <v>15.575699999999999</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
+      <c r="F309">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G309">
+        <v>5.9260000000000002</v>
+      </c>
+      <c r="H309">
+        <v>71</v>
+      </c>
+      <c r="I309">
+        <v>2.9083999999999999</v>
+      </c>
+      <c r="J309">
+        <v>24</v>
+      </c>
+      <c r="K309">
+        <v>666</v>
+      </c>
+      <c r="L309">
+        <v>20.2</v>
+      </c>
+      <c r="M309">
+        <v>368.74</v>
+      </c>
+      <c r="N309">
+        <v>18.13</v>
+      </c>
+      <c r="O309">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A310">
+        <v>470</v>
+      </c>
+      <c r="B310">
+        <v>13.075100000000001</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
+      <c r="F310">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G310">
+        <v>5.7130000000000001</v>
+      </c>
+      <c r="H310">
+        <v>56.7</v>
+      </c>
+      <c r="I310">
+        <v>2.8237000000000001</v>
+      </c>
+      <c r="J310">
+        <v>24</v>
+      </c>
+      <c r="K310">
+        <v>666</v>
+      </c>
+      <c r="L310">
+        <v>20.2</v>
+      </c>
+      <c r="M310">
+        <v>396.9</v>
+      </c>
+      <c r="N310">
+        <v>14.76</v>
+      </c>
+      <c r="O310">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A311">
+        <v>472</v>
+      </c>
+      <c r="B311">
+        <v>4.0384099999999998</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
+      <c r="F311">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="G311">
+        <v>6.2290000000000001</v>
+      </c>
+      <c r="H311">
+        <v>90.7</v>
+      </c>
+      <c r="I311">
+        <v>3.0992999999999999</v>
+      </c>
+      <c r="J311">
+        <v>24</v>
+      </c>
+      <c r="K311">
+        <v>666</v>
+      </c>
+      <c r="L311">
+        <v>20.2</v>
+      </c>
+      <c r="M311">
+        <v>395.33</v>
+      </c>
+      <c r="N311">
+        <v>12.87</v>
+      </c>
+      <c r="O311">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A312">
+        <v>473</v>
+      </c>
+      <c r="B312">
+        <v>3.5686800000000001</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
+      <c r="F312">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G312">
+        <v>6.4370000000000003</v>
+      </c>
+      <c r="H312">
+        <v>75</v>
+      </c>
+      <c r="I312">
+        <v>2.8965000000000001</v>
+      </c>
+      <c r="J312">
+        <v>24</v>
+      </c>
+      <c r="K312">
+        <v>666</v>
+      </c>
+      <c r="L312">
+        <v>20.2</v>
+      </c>
+      <c r="M312">
+        <v>393.37</v>
+      </c>
+      <c r="N312">
+        <v>14.36</v>
+      </c>
+      <c r="O312">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A313">
+        <v>475</v>
+      </c>
+      <c r="B313">
+        <v>8.05579</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
+      <c r="F313">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="G313">
+        <v>5.4269999999999996</v>
+      </c>
+      <c r="H313">
+        <v>95.4</v>
+      </c>
+      <c r="I313">
+        <v>2.4298000000000002</v>
+      </c>
+      <c r="J313">
+        <v>24</v>
+      </c>
+      <c r="K313">
+        <v>666</v>
+      </c>
+      <c r="L313">
+        <v>20.2</v>
+      </c>
+      <c r="M313">
+        <v>352.58</v>
+      </c>
+      <c r="N313">
+        <v>18.14</v>
+      </c>
+      <c r="O313">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A314">
+        <v>477</v>
+      </c>
+      <c r="B314">
+        <v>4.87141</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
+      <c r="F314">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="G314">
+        <v>6.484</v>
+      </c>
+      <c r="H314">
+        <v>93.6</v>
+      </c>
+      <c r="I314">
+        <v>2.3052999999999999</v>
+      </c>
+      <c r="J314">
+        <v>24</v>
+      </c>
+      <c r="K314">
+        <v>666</v>
+      </c>
+      <c r="L314">
+        <v>20.2</v>
+      </c>
+      <c r="M314">
+        <v>396.21</v>
+      </c>
+      <c r="N314">
+        <v>18.68</v>
+      </c>
+      <c r="O314">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A315">
+        <v>478</v>
+      </c>
+      <c r="B315">
+        <v>15.023400000000001</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E315">
+        <v>0</v>
+      </c>
+      <c r="F315">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="G315">
+        <v>5.3040000000000003</v>
+      </c>
+      <c r="H315">
+        <v>97.3</v>
+      </c>
+      <c r="I315">
+        <v>2.1006999999999998</v>
+      </c>
+      <c r="J315">
+        <v>24</v>
+      </c>
+      <c r="K315">
+        <v>666</v>
+      </c>
+      <c r="L315">
+        <v>20.2</v>
+      </c>
+      <c r="M315">
+        <v>349.48</v>
+      </c>
+      <c r="N315">
+        <v>24.91</v>
+      </c>
+      <c r="O315">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A316">
+        <v>479</v>
+      </c>
+      <c r="B316">
+        <v>10.233000000000001</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+      <c r="F316">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="G316">
+        <v>6.1849999999999996</v>
+      </c>
+      <c r="H316">
+        <v>96.7</v>
+      </c>
+      <c r="I316">
+        <v>2.1705000000000001</v>
+      </c>
+      <c r="J316">
+        <v>24</v>
+      </c>
+      <c r="K316">
+        <v>666</v>
+      </c>
+      <c r="L316">
+        <v>20.2</v>
+      </c>
+      <c r="M316">
+        <v>379.7</v>
+      </c>
+      <c r="N316">
+        <v>18.03</v>
+      </c>
+      <c r="O316">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A317">
+        <v>480</v>
+      </c>
+      <c r="B317">
+        <v>14.3337</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E317">
+        <v>0</v>
+      </c>
+      <c r="F317">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="G317">
+        <v>6.2290000000000001</v>
+      </c>
+      <c r="H317">
+        <v>88</v>
+      </c>
+      <c r="I317">
+        <v>1.9512</v>
+      </c>
+      <c r="J317">
+        <v>24</v>
+      </c>
+      <c r="K317">
+        <v>666</v>
+      </c>
+      <c r="L317">
+        <v>20.2</v>
+      </c>
+      <c r="M317">
+        <v>383.32</v>
+      </c>
+      <c r="N317">
+        <v>13.11</v>
+      </c>
+      <c r="O317">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A318">
+        <v>481</v>
+      </c>
+      <c r="B318">
+        <v>5.8240100000000004</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E318">
+        <v>0</v>
+      </c>
+      <c r="F318">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="G318">
+        <v>6.242</v>
+      </c>
+      <c r="H318">
+        <v>64.7</v>
+      </c>
+      <c r="I318">
+        <v>3.4241999999999999</v>
+      </c>
+      <c r="J318">
+        <v>24</v>
+      </c>
+      <c r="K318">
+        <v>666</v>
+      </c>
+      <c r="L318">
+        <v>20.2</v>
+      </c>
+      <c r="M318">
+        <v>396.9</v>
+      </c>
+      <c r="N318">
+        <v>10.74</v>
+      </c>
+      <c r="O318">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A319">
+        <v>482</v>
+      </c>
+      <c r="B319">
+        <v>5.7081799999999996</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E319">
+        <v>0</v>
+      </c>
+      <c r="F319">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="G319">
+        <v>6.75</v>
+      </c>
+      <c r="H319">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="I319">
+        <v>3.3317000000000001</v>
+      </c>
+      <c r="J319">
+        <v>24</v>
+      </c>
+      <c r="K319">
+        <v>666</v>
+      </c>
+      <c r="L319">
+        <v>20.2</v>
+      </c>
+      <c r="M319">
+        <v>393.07</v>
+      </c>
+      <c r="N319">
+        <v>7.74</v>
+      </c>
+      <c r="O319">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A320">
+        <v>484</v>
+      </c>
+      <c r="B320">
+        <v>2.8183799999999999</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
+      <c r="F320">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="G320">
+        <v>5.7619999999999996</v>
+      </c>
+      <c r="H320">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="I320">
+        <v>4.0983000000000001</v>
+      </c>
+      <c r="J320">
+        <v>24</v>
+      </c>
+      <c r="K320">
+        <v>666</v>
+      </c>
+      <c r="L320">
+        <v>20.2</v>
+      </c>
+      <c r="M320">
+        <v>392.92</v>
+      </c>
+      <c r="N320">
+        <v>10.42</v>
+      </c>
+      <c r="O320">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A321">
+        <v>485</v>
+      </c>
+      <c r="B321">
+        <v>2.3785699999999999</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+      <c r="F321">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="G321">
+        <v>5.8710000000000004</v>
+      </c>
+      <c r="H321">
+        <v>41.9</v>
+      </c>
+      <c r="I321">
+        <v>3.7240000000000002</v>
+      </c>
+      <c r="J321">
+        <v>24</v>
+      </c>
+      <c r="K321">
+        <v>666</v>
+      </c>
+      <c r="L321">
+        <v>20.2</v>
+      </c>
+      <c r="M321">
+        <v>370.73</v>
+      </c>
+      <c r="N321">
+        <v>13.34</v>
+      </c>
+      <c r="O321">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A322">
+        <v>487</v>
+      </c>
+      <c r="B322">
+        <v>5.6917499999999999</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
+      <c r="F322">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="G322">
+        <v>6.1139999999999999</v>
+      </c>
+      <c r="H322">
+        <v>79.8</v>
+      </c>
+      <c r="I322">
+        <v>3.5459000000000001</v>
+      </c>
+      <c r="J322">
+        <v>24</v>
+      </c>
+      <c r="K322">
+        <v>666</v>
+      </c>
+      <c r="L322">
+        <v>20.2</v>
+      </c>
+      <c r="M322">
+        <v>392.68</v>
+      </c>
+      <c r="N322">
+        <v>14.98</v>
+      </c>
+      <c r="O322">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A323">
+        <v>488</v>
+      </c>
+      <c r="B323">
+        <v>4.8356700000000004</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
+      <c r="F323">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="G323">
+        <v>5.9050000000000002</v>
+      </c>
+      <c r="H323">
+        <v>53.2</v>
+      </c>
+      <c r="I323">
+        <v>3.1522999999999999</v>
+      </c>
+      <c r="J323">
+        <v>24</v>
+      </c>
+      <c r="K323">
+        <v>666</v>
+      </c>
+      <c r="L323">
+        <v>20.2</v>
+      </c>
+      <c r="M323">
+        <v>388.22</v>
+      </c>
+      <c r="N323">
+        <v>11.45</v>
+      </c>
+      <c r="O323">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A324">
+        <v>489</v>
+      </c>
+      <c r="B324">
+        <v>0.15085999999999999</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>27.74</v>
+      </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
+      <c r="F324">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="G324">
+        <v>5.4539999999999997</v>
+      </c>
+      <c r="H324">
+        <v>92.7</v>
+      </c>
+      <c r="I324">
+        <v>1.8209</v>
+      </c>
+      <c r="J324">
+        <v>4</v>
+      </c>
+      <c r="K324">
+        <v>711</v>
+      </c>
+      <c r="L324">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="M324">
+        <v>395.09</v>
+      </c>
+      <c r="N324">
+        <v>18.059999999999999</v>
+      </c>
+      <c r="O324">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A325">
+        <v>491</v>
+      </c>
+      <c r="B325">
+        <v>0.20746000000000001</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>27.74</v>
+      </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
+      <c r="F325">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="G325">
+        <v>5.093</v>
+      </c>
+      <c r="H325">
+        <v>98</v>
+      </c>
+      <c r="I325">
+        <v>1.8226</v>
+      </c>
+      <c r="J325">
+        <v>4</v>
+      </c>
+      <c r="K325">
+        <v>711</v>
+      </c>
+      <c r="L325">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="M325">
+        <v>318.43</v>
+      </c>
+      <c r="N325">
+        <v>29.68</v>
+      </c>
+      <c r="O325">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A326">
+        <v>492</v>
+      </c>
+      <c r="B326">
+        <v>0.10574</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>27.74</v>
+      </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="G326">
+        <v>5.9829999999999997</v>
+      </c>
+      <c r="H326">
+        <v>98.8</v>
+      </c>
+      <c r="I326">
+        <v>1.8681000000000001</v>
+      </c>
+      <c r="J326">
+        <v>4</v>
+      </c>
+      <c r="K326">
+        <v>711</v>
+      </c>
+      <c r="L326">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="M326">
+        <v>390.11</v>
+      </c>
+      <c r="N326">
+        <v>18.07</v>
+      </c>
+      <c r="O326">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A327">
+        <v>493</v>
+      </c>
+      <c r="B327">
+        <v>0.11132</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>27.74</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="G327">
+        <v>5.9829999999999997</v>
+      </c>
+      <c r="H327">
+        <v>83.5</v>
+      </c>
+      <c r="I327">
+        <v>2.1099000000000001</v>
+      </c>
+      <c r="J327">
+        <v>4</v>
+      </c>
+      <c r="K327">
+        <v>711</v>
+      </c>
+      <c r="L327">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="M327">
+        <v>396.9</v>
+      </c>
+      <c r="N327">
+        <v>13.35</v>
+      </c>
+      <c r="O327">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A328">
+        <v>494</v>
+      </c>
+      <c r="B328">
+        <v>0.17330999999999999</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>9.69</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="G328">
+        <v>5.7069999999999999</v>
+      </c>
+      <c r="H328">
+        <v>54</v>
+      </c>
+      <c r="I328">
+        <v>2.3816999999999999</v>
+      </c>
+      <c r="J328">
+        <v>6</v>
+      </c>
+      <c r="K328">
+        <v>391</v>
+      </c>
+      <c r="L328">
+        <v>19.2</v>
+      </c>
+      <c r="M328">
+        <v>396.9</v>
+      </c>
+      <c r="N328">
+        <v>12.01</v>
+      </c>
+      <c r="O328">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A329">
+        <v>498</v>
+      </c>
+      <c r="B329">
+        <v>0.26838000000000001</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>9.69</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="G329">
+        <v>5.7939999999999996</v>
+      </c>
+      <c r="H329">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="I329">
+        <v>2.8927</v>
+      </c>
+      <c r="J329">
+        <v>6</v>
+      </c>
+      <c r="K329">
+        <v>391</v>
+      </c>
+      <c r="L329">
+        <v>19.2</v>
+      </c>
+      <c r="M329">
+        <v>396.9</v>
+      </c>
+      <c r="N329">
+        <v>14.1</v>
+      </c>
+      <c r="O329">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A330">
+        <v>500</v>
+      </c>
+      <c r="B330">
+        <v>0.17782999999999999</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>9.69</v>
+      </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
+      <c r="F330">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="G330">
+        <v>5.569</v>
+      </c>
+      <c r="H330">
+        <v>73.5</v>
+      </c>
+      <c r="I330">
+        <v>2.3999000000000001</v>
+      </c>
+      <c r="J330">
+        <v>6</v>
+      </c>
+      <c r="K330">
+        <v>391</v>
+      </c>
+      <c r="L330">
+        <v>19.2</v>
+      </c>
+      <c r="M330">
+        <v>395.77</v>
+      </c>
+      <c r="N330">
+        <v>15.1</v>
+      </c>
+      <c r="O330">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A331">
+        <v>502</v>
+      </c>
+      <c r="B331">
+        <v>6.2630000000000005E-2</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>11.93</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+      <c r="F331">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="G331">
+        <v>6.593</v>
+      </c>
+      <c r="H331">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="I331">
+        <v>2.4786000000000001</v>
+      </c>
+      <c r="J331">
+        <v>1</v>
+      </c>
+      <c r="K331">
+        <v>273</v>
+      </c>
+      <c r="L331">
+        <v>21</v>
+      </c>
+      <c r="M331">
+        <v>391.99</v>
+      </c>
+      <c r="N331">
+        <v>9.67</v>
+      </c>
+      <c r="O331">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A332">
+        <v>503</v>
+      </c>
+      <c r="B332">
+        <v>4.5269999999999998E-2</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>11.93</v>
+      </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="G332">
+        <v>6.12</v>
+      </c>
+      <c r="H332">
+        <v>76.7</v>
+      </c>
+      <c r="I332">
+        <v>2.2875000000000001</v>
+      </c>
+      <c r="J332">
+        <v>1</v>
+      </c>
+      <c r="K332">
+        <v>273</v>
+      </c>
+      <c r="L332">
+        <v>21</v>
+      </c>
+      <c r="M332">
+        <v>396.9</v>
+      </c>
+      <c r="N332">
+        <v>9.08</v>
+      </c>
+      <c r="O332">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A333">
+        <v>504</v>
+      </c>
+      <c r="B333">
+        <v>6.0760000000000002E-2</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>11.93</v>
+      </c>
+      <c r="E333">
+        <v>0</v>
+      </c>
+      <c r="F333">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="G333">
+        <v>6.976</v>
+      </c>
+      <c r="H333">
+        <v>91</v>
+      </c>
+      <c r="I333">
+        <v>2.1675</v>
+      </c>
+      <c r="J333">
+        <v>1</v>
+      </c>
+      <c r="K333">
+        <v>273</v>
+      </c>
+      <c r="L333">
+        <v>21</v>
+      </c>
+      <c r="M333">
+        <v>396.9</v>
+      </c>
+      <c r="N333">
+        <v>5.64</v>
+      </c>
+      <c r="O333">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A334">
+        <v>506</v>
+      </c>
+      <c r="B334">
+        <v>4.7410000000000001E-2</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>11.93</v>
+      </c>
+      <c r="E334">
+        <v>0</v>
+      </c>
+      <c r="F334">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="G334">
+        <v>6.03</v>
+      </c>
+      <c r="H334">
+        <v>80.8</v>
+      </c>
+      <c r="I334">
+        <v>2.5049999999999999</v>
+      </c>
+      <c r="J334">
+        <v>1</v>
+      </c>
+      <c r="K334">
+        <v>273</v>
+      </c>
+      <c r="L334">
+        <v>21</v>
+      </c>
+      <c r="M334">
+        <v>396.9</v>
+      </c>
+      <c r="N334">
+        <v>7.88</v>
+      </c>
+      <c r="O334">
+        <v>11.9</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/expRegression.xlsx
+++ b/uploads/expRegression.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/PrediKit/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schir\OneDrive\Studium\34_Github\PrediKit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{77D33F13-5239-4DB2-A715-3512D09D3325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA9603FF-0617-4ACD-9EB7-E1A864B7073A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C048C747-E973-44F0-995D-9D8B3DAC0033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{3FCB8BB5-2836-44B8-913B-2365A2F1C054}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{3FCB8BB5-2836-44B8-913B-2365A2F1C054}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
   <si>
     <t>Author</t>
   </si>
@@ -21037,9 +21037,7 @@
       <c r="N1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="O1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2">
